--- a/tasks/finalpool/arxiv-reading-plan-excel-gcal-email/groundtruth_workspace/Reading_Plan.xlsx
+++ b/tasks/finalpool/arxiv-reading-plan-excel-gcal-email/groundtruth_workspace/Reading_Plan.xlsx
@@ -482,11 +482,13 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>This paper investigates zero-shot communication in LLMs.</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t xml:space="preserve">This paper investigates zero-shot communication capabilities in large language models, finding that </t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -502,7 +504,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Schick, T.; Dwivedi-Yu, J.</t>
+          <t>Schick, T., Dwivedi-Yu, J., Dessi, R., Raileanu, R.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -517,11 +519,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>We introduce Toolformer, a model trained to use tools.</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
+          <t>We introduce Toolformer, a model trained to decide which APIs to call, when to call them, what argum</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -532,12 +536,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HuggingGPT: Solving AI Tasks with ChatGPT</t>
+          <t>HuggingGPT: Solving AI Tasks with ChatGPT and its Friends in Hugging Face</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shen, Y.; Song, K.</t>
+          <t>Shen, Y., Song, K., Tan, X., Li, D.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -552,11 +556,13 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>We propose HuggingGPT using ChatGPT as a controller for AI models.</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
+          <t>We propose HuggingGPT, a system that leverages LLMs like ChatGPT to connect various AI models in Hug</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -567,12 +573,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tree of Thoughts: Deliberate Problem Solving with LLMs</t>
+          <t>Tree of Thoughts: Deliberate Problem Solving with Large Language Models</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yao, S.; Yu, D.</t>
+          <t>Yao, S., Yu, D., Zhao, J., Shafran, I.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,11 +593,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>We introduce Tree of Thoughts for problem solving with LLMs.</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>We introduce Tree of Thoughts (ToT), a framework that allows LLMs to perform deliberate decision mak</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -607,7 +615,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liu, X.; Yu, H.</t>
+          <t>Liu, X., Yu, H., Zhang, H., Xu, Y.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,11 +630,13 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>We present AgentBench for evaluating LLM agents.</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
+          <t>We present AgentBench, a comprehensive benchmark to evaluate LLM-as-Agent across 8 distinct environm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -637,12 +647,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Self-RAG: Learning to Retrieve, Generate, and Critique</t>
+          <t>Self-RAG: Learning to Retrieve, Generate, and Critique through Self-Reflection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Asai, A.; Wu, Z.</t>
+          <t>Asai, A., Wu, Z., Wang, Y., Salehi, H.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -657,11 +667,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>We introduce Self-RAG, a framework to train LLMs to retrieve on demand.</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
+          <t>We introduce Self-RAG, a framework that trains an arbitrary language model to retrieve on demand and</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -672,12 +684,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chain-of-Thought Prompting Elicits Reasoning</t>
+          <t>Chain-of-Thought Prompting Elicits Reasoning in Large Language Models</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wei, J.; Wang, X.</t>
+          <t>Wei, J., Wang, X., Schuurmans, D., Bosma, M.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -692,11 +704,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>We explore chain-of-thought prompting for complex reasoning.</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
+          <t>We explore chain-of-thought prompting as a simple method to elicit multi-step reasoning capabilities</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -712,7 +726,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jiang, A.; Sablayrolles, A.</t>
+          <t>Jiang, A., Sablayrolles, A., Mensch, A., Bamford, C.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -727,11 +741,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>We introduce Mistral 7B, a 7B parameter language model.</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
+          <t>We introduce Mistral 7B, a 7-billion-parameter language model engineered for superior performance an</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -771,142 +787,174 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Large Language Models are not Zero-Shot Communicat...</t>
+          <t>Large Language Models are not Zero-Shot Communicators</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Toolformer: Language Models Can Teach Themselves t...</t>
+          <t>Toolformer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HuggingGPT: Solving AI Tasks with ChatGPT</t>
+          <t>HuggingGPT</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tree of Thoughts: Deliberate Problem Solving with ...</t>
+          <t>Tree of Thoughts</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AgentBench: Evaluating LLMs as Agents</t>
+          <t>AgentBench</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Self-RAG: Learning to Retrieve, Generate, and Crit...</t>
+          <t>Self-RAG</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chain-of-Thought Prompting Elicits Reasoning</t>
+          <t>Chain-of-Thought Prompting Elicits Reasoning in Large Language Models</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
